--- a/output/pdf_financials_xlsx/RMO.xlsx
+++ b/output/pdf_financials_xlsx/RMO.xlsx
@@ -5681,46 +5681,46 @@
         <v>2.063526</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.477035</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.480243</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.487668</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.487668</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.487668</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.99114</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.028043</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.028043</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.028043</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.028043</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.196859</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.196859</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.196859</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.196859</v>
       </c>
     </row>
     <row r="93">
@@ -9238,7 +9238,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10094,7 +10098,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10742,7 +10750,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11700,7 +11712,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -13114,7 +13130,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>2.303985</v>
       </c>

--- a/output/pdf_financials_xlsx/RMO.xlsx
+++ b/output/pdf_financials_xlsx/RMO.xlsx
@@ -2338,19 +2338,19 @@
         <v>0.000671</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.042237</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.362153</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.449424</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.148868</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.025787</v>
       </c>
     </row>
     <row r="35">
@@ -2448,19 +2448,19 @@
         <v>0.000671</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.042237</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.362153</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.449424</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.148868</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.025787</v>
       </c>
     </row>
     <row r="37">
@@ -3108,19 +3108,19 @@
         <v>0.007658</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.050394</v>
+        <v>0.008156999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.365847</v>
+        <v>0.003694</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.454369</v>
+        <v>0.004945</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.153813</v>
+        <v>0.004945</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.030485</v>
+        <v>0.004698</v>
       </c>
     </row>
     <row r="49">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">

--- a/output/pdf_financials_xlsx/RMO.xlsx
+++ b/output/pdf_financials_xlsx/RMO.xlsx
@@ -753,31 +753,31 @@
         <v>0.146797</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.170189</v>
+        <v>0.386342</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.126377</v>
+        <v>0.47819</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.054863</v>
+        <v>0.132988</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.047226</v>
+        <v>0.150476</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.022267</v>
+        <v>0.130267</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.031006</v>
+        <v>0.114506</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.038192</v>
+        <v>0.104192</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.059792</v>
+        <v>0.125792</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07969900000000001</v>
+        <v>0.145699</v>
       </c>
     </row>
     <row r="8">
@@ -933,16 +933,16 @@
         <v>0.03</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.031006</v>
+        <v>0.114506</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.038192</v>
+        <v>0.104192</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.059792</v>
+        <v>0.125792</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.07969900000000001</v>
+        <v>0.145699</v>
       </c>
     </row>
     <row r="11">
@@ -988,16 +988,16 @@
         <v>-0.262239</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.031006</v>
+        <v>-0.114506</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.038192</v>
+        <v>-0.104192</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.059792</v>
+        <v>-0.125792</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.07969900000000001</v>
+        <v>-0.145699</v>
       </c>
     </row>
     <row r="12">
@@ -6696,16 +6696,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017499</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039025</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018795</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031437</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6916,37 +6916,37 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.248365</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.1665</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.139164</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.00457</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.013517</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.058418</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.038061</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.022697</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.00739</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -7997,16 +7997,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017499</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039025</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018795</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031437</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.255297</v>
+        <v>0.237798</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.424407</v>
+        <v>-0.463432</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.039905</v>
+        <v>-0.0587</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.546405</v>
+        <v>-0.577842</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.322605</v>
@@ -18212,7 +18212,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.248365</v>
       </c>
@@ -22364,7 +22368,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -22940,7 +22948,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>-0.017499</v>
       </c>
@@ -23128,7 +23140,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -26080,7 +26096,11 @@
           <t>Consulting and director fees 6</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -27110,7 +27130,11 @@
           <t>Consulting and director fees 7</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -27484,7 +27508,11 @@
           <t>Consulting and director fees (Note 7) $</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -29978,7 +30006,11 @@
           <t>Consulting and director fees (Note 8) $</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
